--- a/Team-Data/2012-13/4-17-2012-13.xlsx
+++ b/Team-Data/2012-13/4-17-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="n">
         <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>0.537</v>
+        <v>0.543</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -679,40 +746,40 @@
         <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>23.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="O2" t="n">
         <v>14.1</v>
       </c>
       <c r="P2" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.715</v>
+        <v>0.713</v>
       </c>
       <c r="R2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="V2" t="n">
         <v>14.9</v>
@@ -730,34 +797,34 @@
         <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB2" t="n">
         <v>98</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>8</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -769,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -787,7 +854,7 @@
         <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
         <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.506</v>
+        <v>0.513</v>
       </c>
       <c r="H3" t="n">
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
         <v>79.7</v>
@@ -876,13 +943,13 @@
         <v>0.358</v>
       </c>
       <c r="O3" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R3" t="n">
         <v>8.1</v>
@@ -891,7 +958,7 @@
         <v>31.3</v>
       </c>
       <c r="T3" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="U3" t="n">
         <v>22.8</v>
@@ -900,7 +967,7 @@
         <v>14.6</v>
       </c>
       <c r="W3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>4.5</v>
@@ -912,13 +979,13 @@
         <v>21.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AD3" t="n">
         <v>29</v>
@@ -951,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
         <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ3" t="n">
         <v>6</v>
@@ -975,7 +1042,7 @@
         <v>12</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -1025,34 +1092,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.598</v>
+        <v>0.593</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
       </c>
       <c r="I4" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
         <v>79.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L4" t="n">
         <v>7.7</v>
       </c>
       <c r="M4" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N4" t="n">
         <v>0.357</v>
@@ -1076,13 +1143,13 @@
         <v>42.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
@@ -1091,13 +1158,13 @@
         <v>4.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC4" t="n">
         <v>1.8</v>
@@ -1106,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
@@ -1118,13 +1185,13 @@
         <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1154,19 +1221,19 @@
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX4" t="n">
         <v>17</v>
       </c>
-      <c r="AW4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>18</v>
-      </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>0.256</v>
+        <v>0.247</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1225,22 +1292,22 @@
         <v>34.4</v>
       </c>
       <c r="J5" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O5" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P5" t="n">
         <v>25.1</v>
@@ -1258,31 +1325,31 @@
         <v>40.3</v>
       </c>
       <c r="U5" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="V5" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
         <v>7.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y5" t="n">
         <v>6.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA5" t="n">
         <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1357,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>0.549</v>
+        <v>0.543</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1410,7 +1477,7 @@
         <v>81.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L6" t="n">
         <v>5.4</v>
@@ -1419,7 +1486,7 @@
         <v>15.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O6" t="n">
         <v>16.4</v>
@@ -1434,10 +1501,10 @@
         <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T6" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U6" t="n">
         <v>23</v>
@@ -1458,7 +1525,7 @@
         <v>19.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB6" t="n">
         <v>93.2</v>
@@ -1470,13 +1537,13 @@
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>13</v>
@@ -1485,13 +1552,13 @@
         <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK6" t="n">
         <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
         <v>29</v>
@@ -1500,13 +1567,13 @@
         <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
         <v>19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1515,16 +1582,16 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
         <v>15</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>0.293</v>
+        <v>0.296</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1592,37 +1659,37 @@
         <v>84.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L7" t="n">
         <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N7" t="n">
         <v>0.346</v>
       </c>
       <c r="O7" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P7" t="n">
         <v>22.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R7" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S7" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T7" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U7" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V7" t="n">
         <v>14</v>
@@ -1634,13 +1701,13 @@
         <v>4.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB7" t="n">
         <v>96.5</v>
@@ -1661,13 +1728,13 @@
         <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>20</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -1685,10 +1752,10 @@
         <v>13</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>7</v>
@@ -1706,7 +1773,7 @@
         <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
         <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.494</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
@@ -1771,10 +1838,10 @@
         <v>38.8</v>
       </c>
       <c r="J8" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L8" t="n">
         <v>7.4</v>
@@ -1786,10 +1853,10 @@
         <v>0.372</v>
       </c>
       <c r="O8" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P8" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0.793</v>
@@ -1801,7 +1868,7 @@
         <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
         <v>23.2</v>
@@ -1816,7 +1883,7 @@
         <v>5.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z8" t="n">
         <v>20.7</v>
@@ -1825,16 +1892,16 @@
         <v>18.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF8" t="n">
         <v>17</v>
@@ -1849,19 +1916,19 @@
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL8" t="n">
         <v>12</v>
       </c>
       <c r="AM8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
         <v>20</v>
@@ -1879,7 +1946,7 @@
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
@@ -1888,7 +1955,7 @@
         <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -1935,25 +2002,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
         <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>0.695</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J9" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.478</v>
@@ -1965,25 +2032,25 @@
         <v>18.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O9" t="n">
         <v>18.4</v>
       </c>
       <c r="P9" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.701</v>
+        <v>0.7</v>
       </c>
       <c r="R9" t="n">
         <v>13.3</v>
       </c>
       <c r="S9" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T9" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U9" t="n">
         <v>24.4</v>
@@ -2001,16 +2068,16 @@
         <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>106.1</v>
+        <v>106</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
@@ -2085,7 +2152,7 @@
         <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2138,7 +2205,7 @@
         <v>81</v>
       </c>
       <c r="K10" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L10" t="n">
         <v>6.3</v>
@@ -2147,16 +2214,16 @@
         <v>17.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.356</v>
+        <v>0.359</v>
       </c>
       <c r="O10" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P10" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="R10" t="n">
         <v>12.1</v>
@@ -2165,16 +2232,16 @@
         <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U10" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X10" t="n">
         <v>4.9</v>
@@ -2183,13 +2250,13 @@
         <v>5.8</v>
       </c>
       <c r="Z10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AA10" t="n">
         <v>19.8</v>
       </c>
-      <c r="AA10" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AB10" t="n">
-        <v>94.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="AC10" t="n">
         <v>-4</v>
@@ -2213,25 +2280,25 @@
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2249,10 +2316,10 @@
         <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>0.573</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J11" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K11" t="n">
         <v>0.458</v>
@@ -2332,10 +2399,10 @@
         <v>0.403</v>
       </c>
       <c r="O11" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P11" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0.79</v>
@@ -2344,10 +2411,10 @@
         <v>10.8</v>
       </c>
       <c r="S11" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="T11" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U11" t="n">
         <v>22.5</v>
@@ -2374,7 +2441,7 @@
         <v>101.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -2392,7 +2459,7 @@
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
@@ -2404,19 +2471,19 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2431,10 +2498,10 @@
         <v>15</v>
       </c>
       <c r="AV11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
         <v>45</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>0.549</v>
+        <v>0.556</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2508,10 +2575,10 @@
         <v>10.6</v>
       </c>
       <c r="M12" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O12" t="n">
         <v>19.2</v>
@@ -2535,7 +2602,7 @@
         <v>23.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W12" t="n">
         <v>8.300000000000001</v>
@@ -2547,16 +2614,16 @@
         <v>6.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>106</v>
+        <v>106.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2571,16 +2638,16 @@
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ12" t="n">
         <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2604,7 +2671,7 @@
         <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2619,19 +2686,19 @@
         <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>9</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" t="n">
         <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>0.605</v>
+        <v>0.613</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2693,16 +2760,16 @@
         <v>19.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O13" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P13" t="n">
         <v>23.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R13" t="n">
         <v>12.9</v>
@@ -2714,7 +2781,7 @@
         <v>45.9</v>
       </c>
       <c r="U13" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V13" t="n">
         <v>15.1</v>
@@ -2723,13 +2790,13 @@
         <v>7.2</v>
       </c>
       <c r="X13" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y13" t="n">
         <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
@@ -2738,7 +2805,7 @@
         <v>94.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
         <v>29</v>
@@ -2759,7 +2826,7 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>26</v>
@@ -2783,7 +2850,7 @@
         <v>19</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS13" t="n">
         <v>5</v>
@@ -2792,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2816,7 +2883,7 @@
         <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2863,7 +2930,7 @@
         <v>38.5</v>
       </c>
       <c r="J14" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
@@ -2872,16 +2939,16 @@
         <v>7.6</v>
       </c>
       <c r="M14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.358</v>
+        <v>0.356</v>
       </c>
       <c r="O14" t="n">
         <v>16.4</v>
       </c>
       <c r="P14" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q14" t="n">
         <v>0.711</v>
@@ -2890,7 +2957,7 @@
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T14" t="n">
         <v>41.6</v>
@@ -2905,7 +2972,7 @@
         <v>9.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y14" t="n">
         <v>4.1</v>
@@ -2917,7 +2984,7 @@
         <v>20.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.1</v>
+        <v>101</v>
       </c>
       <c r="AC14" t="n">
         <v>6.5</v>
@@ -2935,13 +3002,13 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2953,10 +3020,10 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -2965,19 +3032,19 @@
         <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>17</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>9</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F15" t="n">
         <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>0.549</v>
+        <v>0.543</v>
       </c>
       <c r="H15" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I15" t="n">
         <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L15" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O15" t="n">
         <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="Q15" t="n">
         <v>0.6919999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S15" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T15" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V15" t="n">
         <v>15</v>
@@ -3096,40 +3163,40 @@
         <v>17.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
         <v>102.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
         <v>16</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
@@ -3147,10 +3214,10 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
@@ -3159,7 +3226,7 @@
         <v>17</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>25</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" t="n">
         <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.444</v>
@@ -3239,7 +3306,7 @@
         <v>13.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O16" t="n">
         <v>16.5</v>
@@ -3251,13 +3318,13 @@
         <v>0.773</v>
       </c>
       <c r="R16" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S16" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U16" t="n">
         <v>20.9</v>
@@ -3278,13 +3345,13 @@
         <v>20.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
@@ -3305,7 +3372,7 @@
         <v>23</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>21</v>
@@ -3323,19 +3390,19 @@
         <v>16</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS16" t="n">
         <v>24</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>24</v>
@@ -3347,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3359,10 +3426,10 @@
         <v>13</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -3391,67 +3458,67 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.805</v>
+        <v>0.802</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J17" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.496</v>
+        <v>0.495</v>
       </c>
       <c r="L17" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
         <v>0.396</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S17" t="n">
         <v>30.4</v>
       </c>
       <c r="T17" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="U17" t="n">
         <v>23</v>
       </c>
       <c r="V17" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W17" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y17" t="n">
         <v>3.2</v>
@@ -3466,7 +3533,7 @@
         <v>102.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3508,19 +3575,19 @@
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -3573,22 +3640,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F18" t="n">
         <v>44</v>
       </c>
       <c r="G18" t="n">
-        <v>0.463</v>
+        <v>0.457</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J18" t="n">
         <v>87.8</v>
@@ -3600,7 +3667,7 @@
         <v>7.3</v>
       </c>
       <c r="M18" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N18" t="n">
         <v>0.36</v>
@@ -3609,7 +3676,7 @@
         <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.736</v>
@@ -3621,7 +3688,7 @@
         <v>30.9</v>
       </c>
       <c r="T18" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U18" t="n">
         <v>22.9</v>
@@ -3633,7 +3700,7 @@
         <v>8.4</v>
       </c>
       <c r="X18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y18" t="n">
         <v>4.4</v>
@@ -3642,13 +3709,13 @@
         <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB18" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AD18" t="n">
         <v>1</v>
@@ -3666,7 +3733,7 @@
         <v>13</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3675,13 +3742,13 @@
         <v>28</v>
       </c>
       <c r="AL18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN18" t="n">
         <v>13</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>26</v>
@@ -3720,13 +3787,13 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -3755,43 +3822,43 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
         <v>51</v>
       </c>
       <c r="G19" t="n">
-        <v>0.378</v>
+        <v>0.37</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J19" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0.439</v>
       </c>
       <c r="L19" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.305</v>
+        <v>0.303</v>
       </c>
       <c r="O19" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P19" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q19" t="n">
         <v>0.742</v>
@@ -3800,13 +3867,13 @@
         <v>11.9</v>
       </c>
       <c r="S19" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T19" t="n">
         <v>42</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V19" t="n">
         <v>14.8</v>
@@ -3815,7 +3882,7 @@
         <v>8.5</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
         <v>5.9</v>
@@ -3827,10 +3894,10 @@
         <v>22.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
         <v>1</v>
@@ -3845,22 +3912,22 @@
         <v>22</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
@@ -3875,7 +3942,7 @@
         <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
         <v>19</v>
@@ -3890,7 +3957,7 @@
         <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
         <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J20" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L20" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N20" t="n">
         <v>0.363</v>
       </c>
       <c r="O20" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0.776</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S20" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T20" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="U20" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V20" t="n">
         <v>14.5</v>
       </c>
       <c r="W20" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X20" t="n">
         <v>5.4</v>
@@ -4009,10 +4076,10 @@
         <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD20" t="n">
         <v>1</v>
@@ -4036,16 +4103,16 @@
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
       </c>
       <c r="AM20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO20" t="n">
         <v>25</v>
@@ -4054,28 +4121,28 @@
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
         <v>23</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
         <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
         <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>0.659</v>
+        <v>0.654</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,7 +4204,7 @@
         <v>36.5</v>
       </c>
       <c r="J21" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K21" t="n">
         <v>0.448</v>
@@ -4146,31 +4213,31 @@
         <v>10.9</v>
       </c>
       <c r="M21" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="N21" t="n">
         <v>0.376</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P21" t="n">
         <v>21.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
         <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="U21" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V21" t="n">
         <v>12</v>
@@ -4185,10 +4252,10 @@
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB21" t="n">
         <v>100</v>
@@ -4209,16 +4276,16 @@
         <v>7</v>
       </c>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO21" t="n">
         <v>21</v>
@@ -4236,10 +4303,10 @@
         <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS21" t="n">
         <v>25</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
         <v>60</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.732</v>
+        <v>0.741</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,25 +4386,25 @@
         <v>38.1</v>
       </c>
       <c r="J22" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.481</v>
+        <v>0.482</v>
       </c>
       <c r="L22" t="n">
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="O22" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="P22" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q22" t="n">
         <v>0.828</v>
@@ -4346,7 +4413,7 @@
         <v>10.4</v>
       </c>
       <c r="S22" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T22" t="n">
         <v>43.6</v>
@@ -4355,13 +4422,13 @@
         <v>21.4</v>
       </c>
       <c r="V22" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W22" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="Y22" t="n">
         <v>3.9</v>
@@ -4370,13 +4437,13 @@
         <v>20.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.7</v>
+        <v>105.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4403,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM22" t="n">
         <v>16</v>
@@ -4424,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4433,10 +4500,10 @@
         <v>21</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4445,7 +4512,7 @@
         <v>2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
         <v>8</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
-        <v>0.244</v>
+        <v>0.247</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,34 +4568,34 @@
         <v>37.7</v>
       </c>
       <c r="J23" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L23" t="n">
         <v>6.2</v>
       </c>
       <c r="M23" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.329</v>
+        <v>0.331</v>
       </c>
       <c r="O23" t="n">
         <v>12.5</v>
       </c>
       <c r="P23" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.755</v>
+        <v>0.761</v>
       </c>
       <c r="R23" t="n">
         <v>10.9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
         <v>42.7</v>
@@ -4540,7 +4607,7 @@
         <v>14.5</v>
       </c>
       <c r="W23" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X23" t="n">
         <v>4.4</v>
@@ -4558,19 +4625,19 @@
         <v>94.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
@@ -4579,19 +4646,19 @@
         <v>10</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM23" t="n">
         <v>18</v>
       </c>
       <c r="AN23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>19</v>
@@ -4609,19 +4676,19 @@
         <v>9</v>
       </c>
       <c r="AT23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV23" t="n">
         <v>12</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>29</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY23" t="n">
         <v>18</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
         <v>48</v>
       </c>
       <c r="G24" t="n">
-        <v>0.415</v>
+        <v>0.407</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J24" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L24" t="n">
         <v>6.3</v>
@@ -4695,10 +4762,10 @@
         <v>17.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O24" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="P24" t="n">
         <v>16.8</v>
@@ -4716,7 +4783,7 @@
         <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V24" t="n">
         <v>13</v>
@@ -4731,16 +4798,16 @@
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD24" t="n">
         <v>1</v>
@@ -4755,25 +4822,25 @@
         <v>19</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ24" t="n">
         <v>7</v>
       </c>
       <c r="AK24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" t="n">
         <v>22</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>21</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,13 +4855,13 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4806,7 +4873,7 @@
         <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" t="n">
         <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" t="n">
-        <v>0.305</v>
+        <v>0.309</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4865,40 +4932,40 @@
         <v>37.3</v>
       </c>
       <c r="J25" t="n">
-        <v>84.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.443</v>
       </c>
       <c r="L25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M25" t="n">
         <v>17.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O25" t="n">
         <v>14.7</v>
       </c>
       <c r="P25" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R25" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T25" t="n">
         <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V25" t="n">
         <v>15.6</v>
@@ -4916,13 +4983,13 @@
         <v>20.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.5</v>
+        <v>-6.3</v>
       </c>
       <c r="AD25" t="n">
         <v>1</v>
@@ -4943,10 +5010,10 @@
         <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL25" t="n">
         <v>26</v>
@@ -4955,7 +5022,7 @@
         <v>23</v>
       </c>
       <c r="AN25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO25" t="n">
         <v>27</v>
@@ -4970,7 +5037,7 @@
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>18</v>
@@ -4985,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G26" t="n">
-        <v>0.402</v>
+        <v>0.407</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5056,16 +5123,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="N26" t="n">
         <v>0.353</v>
       </c>
       <c r="O26" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0.776</v>
@@ -5074,7 +5141,7 @@
         <v>10.7</v>
       </c>
       <c r="S26" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T26" t="n">
         <v>40.8</v>
@@ -5095,28 +5162,28 @@
         <v>4.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>8</v>
@@ -5140,13 +5207,13 @@
         <v>20</v>
       </c>
       <c r="AO26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
         <v>24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR26" t="n">
         <v>23</v>
@@ -5155,13 +5222,13 @@
         <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU26" t="n">
         <v>18</v>
       </c>
       <c r="AV26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW26" t="n">
         <v>28</v>
@@ -5170,7 +5237,7 @@
         <v>26</v>
       </c>
       <c r="AY26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="n">
         <v>28</v>
       </c>
       <c r="F27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" t="n">
-        <v>0.341</v>
+        <v>0.346</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,7 +5296,7 @@
         <v>37.6</v>
       </c>
       <c r="J27" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.447</v>
@@ -5238,7 +5305,7 @@
         <v>7.4</v>
       </c>
       <c r="M27" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N27" t="n">
         <v>0.363</v>
@@ -5256,16 +5323,16 @@
         <v>11.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T27" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U27" t="n">
         <v>20.8</v>
       </c>
       <c r="V27" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W27" t="n">
         <v>8.199999999999999</v>
@@ -5277,13 +5344,13 @@
         <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
         <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="AC27" t="n">
         <v>-4.9</v>
@@ -5304,10 +5371,10 @@
         <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK27" t="n">
         <v>19</v>
@@ -5319,13 +5386,13 @@
         <v>10</v>
       </c>
       <c r="AN27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO27" t="n">
         <v>10</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>11</v>
@@ -5343,10 +5410,10 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -5393,34 +5460,34 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" t="n">
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>0.707</v>
+        <v>0.716</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J28" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.481</v>
+        <v>0.482</v>
       </c>
       <c r="L28" t="n">
         <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="N28" t="n">
         <v>0.376</v>
@@ -5432,19 +5499,19 @@
         <v>21</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.791</v>
+        <v>0.789</v>
       </c>
       <c r="R28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T28" t="n">
         <v>41.3</v>
       </c>
       <c r="U28" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
@@ -5453,22 +5520,22 @@
         <v>8.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AA28" t="n">
         <v>19.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>103</v>
+        <v>103.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5501,16 +5568,16 @@
         <v>7</v>
       </c>
       <c r="AN28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5519,16 +5586,16 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
         <v>9</v>
@@ -5540,13 +5607,13 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
       </c>
       <c r="BC28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F29" t="n">
         <v>48</v>
       </c>
       <c r="G29" t="n">
-        <v>0.415</v>
+        <v>0.407</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
@@ -5596,19 +5663,19 @@
         <v>81.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M29" t="n">
         <v>20.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="O29" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P29" t="n">
         <v>22.3</v>
@@ -5620,10 +5687,10 @@
         <v>10.6</v>
       </c>
       <c r="S29" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
         <v>21.5</v>
@@ -5638,19 +5705,19 @@
         <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA29" t="n">
         <v>20.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.2</v>
+        <v>97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.5</v>
+        <v>-1.8</v>
       </c>
       <c r="AD29" t="n">
         <v>1</v>
@@ -5668,10 +5735,10 @@
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK29" t="n">
         <v>20</v>
@@ -5680,16 +5747,16 @@
         <v>15</v>
       </c>
       <c r="AM29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN29" t="n">
         <v>26</v>
       </c>
       <c r="AO29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ29" t="n">
         <v>5</v>
@@ -5698,7 +5765,7 @@
         <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5710,10 +5777,10 @@
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5728,7 +5795,7 @@
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -5757,49 +5824,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E30" t="n">
         <v>43</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>0.524</v>
+        <v>0.531</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>37.1</v>
+        <v>37.3</v>
       </c>
       <c r="J30" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L30" t="n">
         <v>6.2</v>
       </c>
       <c r="M30" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N30" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O30" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P30" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R30" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S30" t="n">
         <v>30</v>
@@ -5808,7 +5875,7 @@
         <v>42</v>
       </c>
       <c r="U30" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V30" t="n">
         <v>14.8</v>
@@ -5820,19 +5887,19 @@
         <v>6.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>98</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5850,7 +5917,7 @@
         <v>5</v>
       </c>
       <c r="AI30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
         <v>12</v>
@@ -5865,10 +5932,10 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO30" t="n">
         <v>8</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>9</v>
       </c>
       <c r="AP30" t="n">
         <v>11</v>
@@ -5883,7 +5950,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
         <v>13</v>
@@ -5898,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E31" t="n">
         <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G31" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
@@ -5966,10 +6033,10 @@
         <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O31" t="n">
         <v>15.6</v>
@@ -5978,22 +6045,22 @@
         <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S31" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T31" t="n">
         <v>43.2</v>
       </c>
       <c r="U31" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V31" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
@@ -6053,28 +6120,28 @@
         <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ31" t="n">
         <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
         <v>19</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
         <v>21</v>
@@ -6086,13 +6153,13 @@
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>28</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-17-2012-13</t>
+          <t>2013-04-17</t>
         </is>
       </c>
     </row>
